--- a/OpenCart-Test_Cases.xlsx
+++ b/OpenCart-Test_Cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/15d74eb5e75247de/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/15d74eb5e75247de/Desktop/SQA_Projects/ManualTesting_OpenCart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{07E07010-6A85-49ED-BD2A-DE620145CABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5085E492-0147-4771-9E22-2EEEBD3738FF}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{07E07010-6A85-49ED-BD2A-DE620145CABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF4E9770-74F2-483A-86E2-DF14C407C963}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{D783FD90-809F-4B44-936B-AE99B681FA9D}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="216">
   <si>
     <t>Project Name</t>
   </si>
@@ -49,44 +49,717 @@
     <t>Test Case ID</t>
   </si>
   <si>
-    <t>Test Scenario</t>
-  </si>
-  <si>
     <t>Test Case Title</t>
   </si>
   <si>
-    <t>Pre-requisites</t>
-  </si>
-  <si>
-    <t>Test Steps</t>
-  </si>
-  <si>
-    <t>Test Data</t>
-  </si>
-  <si>
-    <t>TC_RF_001</t>
-  </si>
-  <si>
-    <t>TC_RF_002</t>
-  </si>
-  <si>
-    <t>TC_RF_003</t>
-  </si>
-  <si>
     <t>TS_001</t>
   </si>
   <si>
-    <t>Validate registering an account by providing only the mandatory fields</t>
+    <t>TC_001</t>
+  </si>
+  <si>
+    <t>Register a new account with all valid mandatory details</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>OpenCart Register Account page</t>
+  </si>
+  <si>
+    <t>1. Open My Account &gt; Register
+2. Enter unique valid first/last name, email, telephone and password
+3. Confirm password
+4. Accept Privacy Policy
+5. Click Continue</t>
+  </si>
+  <si>
+    <t>Account is created successfully and confirmation page is displayed.</t>
+  </si>
+  <si>
+    <t>TC_002</t>
+  </si>
+  <si>
+    <t>Register with an already registered email address</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>Register Account page</t>
+  </si>
+  <si>
+    <t>1. Enter valid registration data
+2. Use an email already associated with an account
+3. Accept Privacy Policy
+4. Click Continue</t>
+  </si>
+  <si>
+    <t>Registration is rejected and a clear duplicate-email message is shown.</t>
+  </si>
+  <si>
+    <t>TC_003</t>
+  </si>
+  <si>
+    <t>Register without accepting Privacy Policy</t>
+  </si>
+  <si>
+    <t>1. Fill valid registration fields
+2. Leave Privacy Policy unchecked
+3. Click Continue</t>
+  </si>
+  <si>
+    <t>Registration is blocked and the Privacy Policy validation message is displayed.</t>
+  </si>
+  <si>
+    <t>TC_004</t>
+  </si>
+  <si>
+    <t>TS_002</t>
+  </si>
+  <si>
+    <t>Login with valid credentials</t>
+  </si>
+  <si>
+    <t>Login page</t>
+  </si>
+  <si>
+    <t>1. Open My Account &gt; Login
+2. Enter valid email and password
+3. Click Login</t>
+  </si>
+  <si>
+    <t>User is authenticated and redirected to the account area.</t>
+  </si>
+  <si>
+    <t>TC_005</t>
+  </si>
+  <si>
+    <t>Login with invalid password</t>
+  </si>
+  <si>
+    <t>1. Enter a registered email
+2. Enter an incorrect password
+3. Click Login</t>
+  </si>
+  <si>
+    <t>Login fails and an appropriate authentication error is displayed.</t>
+  </si>
+  <si>
+    <t>TC_006</t>
+  </si>
+  <si>
+    <t>TS_003</t>
+  </si>
+  <si>
+    <t>Logout from an authenticated account</t>
+  </si>
+  <si>
+    <t>Account area</t>
+  </si>
+  <si>
+    <t>1. Log in
+2. Click My Account &gt; Logout</t>
+  </si>
+  <si>
+    <t>User is logged out and returned to the logout confirmation/home area.</t>
+  </si>
+  <si>
+    <t>TC_007</t>
+  </si>
+  <si>
+    <t>TS_004</t>
+  </si>
+  <si>
+    <t>Request password reset for a registered email</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Forgotten Password page</t>
+  </si>
+  <si>
+    <t>1. Open Login
+2. Click Forgotten Password
+3. Enter a registered email
+4. Submit</t>
+  </si>
+  <si>
+    <t>Reset request is accepted and the application displays an appropriate confirmation message.</t>
+  </si>
+  <si>
+    <t>TC_008</t>
+  </si>
+  <si>
+    <t>TC_009</t>
+  </si>
+  <si>
+    <t>TC_010</t>
+  </si>
+  <si>
+    <t>TC_011</t>
+  </si>
+  <si>
+    <t>TC_012</t>
+  </si>
+  <si>
+    <t>TC_013</t>
+  </si>
+  <si>
+    <t>TC_014</t>
+  </si>
+  <si>
+    <t>TC_015</t>
+  </si>
+  <si>
+    <t>TC_016</t>
+  </si>
+  <si>
+    <t>TC_017</t>
+  </si>
+  <si>
+    <t>TC_018</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>TS_005</t>
+  </si>
+  <si>
+    <t>Search using an exact product name</t>
+  </si>
+  <si>
+    <t>Search bar</t>
+  </si>
+  <si>
+    <t>1. Enter a known product name
+2. Click Search</t>
+  </si>
+  <si>
+    <t>Relevant matching product(s) are returned.</t>
+  </si>
+  <si>
+    <t>Search using a partial product keyword</t>
+  </si>
+  <si>
+    <t>1. Enter part of a known product name
+2. Submit search</t>
+  </si>
+  <si>
+    <t>Products matching the keyword are displayed.</t>
+  </si>
+  <si>
+    <t>TS_006</t>
+  </si>
+  <si>
+    <t>Add a product to Product Compare</t>
+  </si>
+  <si>
+    <t>Product listing/details</t>
+  </si>
+  <si>
+    <t>1. Open a product listing
+2. Click Compare for a product
+3. Open the comparison page</t>
+  </si>
+  <si>
+    <t>Selected product appears in the comparison list.</t>
+  </si>
+  <si>
+    <t>Compare two products</t>
+  </si>
+  <si>
+    <t>Product Compare page</t>
+  </si>
+  <si>
+    <t>1. Add two comparable products
+2. Open Product Compare</t>
+  </si>
+  <si>
+    <t>Both products appear side by side with their available attributes.</t>
+  </si>
+  <si>
+    <t>TS_007</t>
+  </si>
+  <si>
+    <t>Verify product details page</t>
+  </si>
+  <si>
+    <t>Product details page</t>
+  </si>
+  <si>
+    <t>1. Open a product
+2. Review name, image, price and description</t>
+  </si>
+  <si>
+    <t>Correct product information is displayed without broken layout/content.</t>
+  </si>
+  <si>
+    <t>Verify product listing pagination/sorting</t>
+  </si>
+  <si>
+    <t>Category/product listing</t>
+  </si>
+  <si>
+    <t>1. Open a category with multiple products
+2. Change sort/order or navigate pages</t>
+  </si>
+  <si>
+    <t>Listing updates according to the selected sort/page without losing product context.</t>
+  </si>
+  <si>
+    <t>TS_008</t>
+  </si>
+  <si>
+    <t>Add a product to cart from product page</t>
+  </si>
+  <si>
+    <t>1. Open a product
+2. Click Add to Cart</t>
+  </si>
+  <si>
+    <t>Product is added and cart count/confirmation reflects the addition.</t>
+  </si>
+  <si>
+    <t>Add multiple different products to cart</t>
+  </si>
+  <si>
+    <t>Product details/cart</t>
+  </si>
+  <si>
+    <t>1. Add product A
+2. Return to listing
+3. Add product B
+4. Open cart</t>
+  </si>
+  <si>
+    <t>Both products are present with correct names and quantities.</t>
+  </si>
+  <si>
+    <t>TS_009</t>
+  </si>
+  <si>
+    <t>Add a product to wishlist while logged in</t>
+  </si>
+  <si>
+    <t>1. Log in
+2. Select Add to Wish List for a product
+3. Open Wishlist</t>
+  </si>
+  <si>
+    <t>Product appears in the user's wishlist.</t>
+  </si>
+  <si>
+    <t>TS_010</t>
+  </si>
+  <si>
+    <t>Update product quantity in shopping cart</t>
+  </si>
+  <si>
+    <t>Shopping Cart</t>
+  </si>
+  <si>
+    <t>1. Add a product
+2. Open Cart
+3. Change quantity
+4. Click Update</t>
+  </si>
+  <si>
+    <t>Quantity and totals update correctly.</t>
+  </si>
+  <si>
+    <t>Remove a product from shopping cart</t>
+  </si>
+  <si>
+    <t>1. Add a product
+2. Open Cart
+3. Click Remove</t>
+  </si>
+  <si>
+    <t>Product is removed and cart totals/count are updated.</t>
+  </si>
+  <si>
+    <t>TC_019</t>
+  </si>
+  <si>
+    <t>Verify cart subtotal, tax and total calculations</t>
+  </si>
+  <si>
+    <t>Calculation</t>
+  </si>
+  <si>
+    <t>1. Add product(s)
+2. Review price, quantity, subtotal and total values</t>
+  </si>
+  <si>
+    <t>Displayed totals are calculated consistently from item prices, quantities and applicable charges.</t>
+  </si>
+  <si>
+    <t>TC_020</t>
+  </si>
+  <si>
+    <t>TS_011</t>
+  </si>
+  <si>
+    <t>Verify home page navigation and featured content</t>
+  </si>
+  <si>
+    <t>Home page</t>
+  </si>
+  <si>
+    <t>1. Open home page
+2. Verify logo, navigation, featured products and key links
+3. Click selected links</t>
+  </si>
+  <si>
+    <t>Home page loads correctly and links navigate to the intended destinations.</t>
+  </si>
+  <si>
+    <t>TC_021</t>
+  </si>
+  <si>
+    <t>TS_012</t>
+  </si>
+  <si>
+    <t>Complete checkout for a logged-in customer</t>
+  </si>
+  <si>
+    <t>End-to-End</t>
+  </si>
+  <si>
+    <t>Checkout</t>
+  </si>
+  <si>
+    <t>1. Log in
+2. Add product to cart
+3. Proceed to checkout
+4. Complete required checkout steps
+5. Confirm order</t>
+  </si>
+  <si>
+    <t>Order is placed successfully and an order confirmation is displayed.</t>
+  </si>
+  <si>
+    <t>TC_022</t>
+  </si>
+  <si>
+    <t>Checkout validation with required fields missing</t>
+  </si>
+  <si>
+    <t>1. Add product to cart
+2. Proceed to checkout
+3. Leave required customer/address fields empty
+4. Continue</t>
+  </si>
+  <si>
+    <t>Checkout does not proceed and field-level validation messages are displayed.</t>
+  </si>
+  <si>
+    <t>TC_023</t>
+  </si>
+  <si>
+    <t>TS_013</t>
+  </si>
+  <si>
+    <t>Open My Account dashboard after login</t>
+  </si>
+  <si>
+    <t>My Account</t>
+  </si>
+  <si>
+    <t>1. Log in
+2. Open My Account</t>
+  </si>
+  <si>
+    <t>Account dashboard and available account/order links are displayed.</t>
+  </si>
+  <si>
+    <t>TC_024</t>
+  </si>
+  <si>
+    <t>TS_014</t>
+  </si>
+  <si>
+    <t>Update account information</t>
+  </si>
+  <si>
+    <t>Account Information</t>
+  </si>
+  <si>
+    <t>1. Log in
+2. Open Account Information
+3. Change an editable field
+4. Save</t>
+  </si>
+  <si>
+    <t>Updated information is saved and confirmation is displayed.</t>
+  </si>
+  <si>
+    <t>TC_025</t>
+  </si>
+  <si>
+    <t>TS_015</t>
+  </si>
+  <si>
+    <t>Change password with correct current password</t>
+  </si>
+  <si>
+    <t>Change Password</t>
+  </si>
+  <si>
+    <t>1. Log in
+2. Open Change Password
+3. Enter current password and matching new password
+4. Save</t>
+  </si>
+  <si>
+    <t>Password is changed successfully and confirmation is displayed.</t>
+  </si>
+  <si>
+    <t>TC_026</t>
+  </si>
+  <si>
+    <t>TS_016</t>
+  </si>
+  <si>
+    <t>Add and edit an address in Address Book</t>
+  </si>
+  <si>
+    <t>Address Book</t>
+  </si>
+  <si>
+    <t>1. Log in
+2. Open Address Book
+3. Add a valid address
+4. Edit it and save</t>
+  </si>
+  <si>
+    <t>Address is added/updated and displayed correctly in the address book.</t>
+  </si>
+  <si>
+    <t>TC_027</t>
+  </si>
+  <si>
+    <t>TS_017</t>
+  </si>
+  <si>
+    <t>Verify Order History after placing an order</t>
+  </si>
+  <si>
+    <t>Order History</t>
+  </si>
+  <si>
+    <t>1. Log in after completing an order
+2. Open Order History</t>
+  </si>
+  <si>
+    <t>Recent order is listed with order number, date, status and total.</t>
+  </si>
+  <si>
+    <t>TC_028</t>
+  </si>
+  <si>
+    <t>TS_018</t>
+  </si>
+  <si>
+    <t>Open order details from Order History</t>
+  </si>
+  <si>
+    <t>Order Information</t>
+  </si>
+  <si>
+    <t>1. Open Order History
+2. Select an order
+3. View order details</t>
+  </si>
+  <si>
+    <t>Order information shows correct products, quantities, totals, billing/shipping details and status.</t>
+  </si>
+  <si>
+    <t>TC_029</t>
+  </si>
+  <si>
+    <t>TS_019</t>
+  </si>
+  <si>
+    <t>Submit a product return request</t>
+  </si>
+  <si>
+    <t>Product Returns</t>
+  </si>
+  <si>
+    <t>1. Log in
+2. Open Product Returns
+3. Select an eligible order/product
+4. Enter required return details
+5. Submit</t>
+  </si>
+  <si>
+    <t>Return request is accepted and confirmation/reference information is shown.</t>
+  </si>
+  <si>
+    <t>TC_030</t>
+  </si>
+  <si>
+    <t>TS_020</t>
+  </si>
+  <si>
+    <t>Verify Downloads area for an account</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Downloads</t>
+  </si>
+  <si>
+    <t>1. Log in
+2. Open Downloads</t>
+  </si>
+  <si>
+    <t>Downloads page loads and displays available downloads or an appropriate empty-state message.</t>
+  </si>
+  <si>
+    <t>TC_031</t>
+  </si>
+  <si>
+    <t>TS_021</t>
+  </si>
+  <si>
+    <t>Verify Reward Points area</t>
+  </si>
+  <si>
+    <t>Reward Points</t>
+  </si>
+  <si>
+    <t>1. Log in
+2. Open Reward Points</t>
+  </si>
+  <si>
+    <t>Reward points page loads and displays the account's available points/history or an appropriate empty-state message.</t>
+  </si>
+  <si>
+    <t>TC_032</t>
+  </si>
+  <si>
+    <t>TS_022</t>
+  </si>
+  <si>
+    <t>Verify Returned Requests area</t>
+  </si>
+  <si>
+    <t>Returned Requests</t>
+  </si>
+  <si>
+    <t>1. Log in
+2. Open Returned Requests</t>
+  </si>
+  <si>
+    <t>Returned request list loads and displays available requests or an appropriate empty-state message.</t>
+  </si>
+  <si>
+    <t>TC_033</t>
+  </si>
+  <si>
+    <t>TS_023</t>
+  </si>
+  <si>
+    <t>Verify Transactions area</t>
+  </si>
+  <si>
+    <t>Transactions</t>
+  </si>
+  <si>
+    <t>1. Log in
+2. Open Transactions</t>
+  </si>
+  <si>
+    <t>Transaction history loads and displays available transactions or an appropriate empty-state message.</t>
+  </si>
+  <si>
+    <t>TC_034</t>
+  </si>
+  <si>
+    <t>TS_024</t>
+  </si>
+  <si>
+    <t>Verify Recurring Payments area</t>
+  </si>
+  <si>
+    <t>Recurring Payments</t>
+  </si>
+  <si>
+    <t>1. Log in
+2. Open Recurring Payments</t>
+  </si>
+  <si>
+    <t>Recurring payments page loads and displays active plans/history or an appropriate empty-state message.</t>
+  </si>
+  <si>
+    <t>TC_035</t>
+  </si>
+  <si>
+    <t>TS_026</t>
+  </si>
+  <si>
+    <t>Update newsletter subscription preference</t>
+  </si>
+  <si>
+    <t>Newsletter / Account</t>
+  </si>
+  <si>
+    <t>1. Log in
+2. Open newsletter preference
+3. Change subscription option
+4. Save</t>
+  </si>
+  <si>
+    <t>Newsletter preference is saved and confirmation is displayed.</t>
+  </si>
+  <si>
+    <t>Test Scenario ID</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Steps to Execute</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Execution Status</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -118,7 +791,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -126,6 +799,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -479,341 +1158,1096 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A39B6A5-0966-456B-9595-6CF27E82DECE}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="57.5703125" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+    <col min="6" max="6" width="31.7109375" customWidth="1"/>
+    <col min="7" max="7" width="31.85546875" customWidth="1"/>
+    <col min="8" max="8" width="48.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="K2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="I3" s="3"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="I5" s="3"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="K5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="K6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="K7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="K8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="K9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="K10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>73</v>
+      </c>
       <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="K11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="K12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="I13" s="3"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="K13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="K14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>90</v>
+      </c>
       <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="K15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>94</v>
+      </c>
       <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="K16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="K17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="K18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>106</v>
+      </c>
       <c r="I19" s="3"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+      <c r="K19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>111</v>
+      </c>
       <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="K20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>117</v>
+      </c>
       <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="K21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+      <c r="K22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="K23" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
+      <c r="K24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="I25" s="3"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
+      <c r="K25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="I26" s="3"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="K26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>147</v>
+      </c>
+      <c r="B27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>150</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="K27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>153</v>
+      </c>
+      <c r="B28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>156</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="K28" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>162</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="K29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>165</v>
+      </c>
+      <c r="B30" t="s">
+        <v>166</v>
+      </c>
+      <c r="C30" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>168</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="K30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B31" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" t="s">
+        <v>173</v>
+      </c>
+      <c r="D31" t="s">
+        <v>174</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s">
+        <v>175</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="K31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>178</v>
+      </c>
+      <c r="B32" t="s">
+        <v>179</v>
+      </c>
+      <c r="C32" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" t="s">
+        <v>174</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>181</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="K32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>184</v>
+      </c>
+      <c r="B33" t="s">
+        <v>185</v>
+      </c>
+      <c r="C33" t="s">
+        <v>186</v>
+      </c>
+      <c r="D33" t="s">
+        <v>174</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>187</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="K33" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>190</v>
+      </c>
+      <c r="B34" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" t="s">
+        <v>192</v>
+      </c>
+      <c r="D34" t="s">
+        <v>174</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>193</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="K34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>196</v>
+      </c>
+      <c r="B35" t="s">
+        <v>197</v>
+      </c>
+      <c r="C35" t="s">
+        <v>198</v>
+      </c>
+      <c r="D35" t="s">
+        <v>174</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>199</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="K35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>202</v>
+      </c>
+      <c r="B36" t="s">
+        <v>203</v>
+      </c>
+      <c r="C36" t="s">
+        <v>204</v>
+      </c>
+      <c r="D36" t="s">
+        <v>174</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>205</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="K36" t="s">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>